--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -425,100 +425,262 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>src</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source_text</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>target_text</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>repetition</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ice_match</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>in_scope</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>mt</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>qe_score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>file_with_formatting.docx</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NFDBB2FA9-tu1_0</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>This is a &lt;g1&gt;bolded&lt;/g1&gt; word.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0.5071799755096436</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>file_with_formatting.docx</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NFDBB2FA9-tu2_0</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>This is my best sentence yet.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>0.8854201436042786</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>هذه أفضل جملة لي حتى الآن.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>foo.xml</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1_0</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>This is a repeated sentence.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0.910571277141571</v>
-      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>هذه جملة مكررة.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>foo.xml</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2_0</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>The following is addressed to a girl:</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>يتم توجيه ما يلي إلى فتاة:</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0.8859434723854065</v>
-      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ما يلي موجه إلى فتاة:</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>foo.xml</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3_0</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>What is your age?</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>كم عمرك ؟</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0.9172203540802002</v>
-      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FIRST</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>كم عمرك؟</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
+          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -513,10 +513,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>هذه كلمة بخط &lt;g1&gt;غامق&lt;/g1&gt;.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8085042834281921</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,7 +556,9 @@
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.8854201436042786</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -596,7 +600,9 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.9105713367462158</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -619,7 +625,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>يتم توجيه ما يلي إلى فتاة:</t>
+          <t>ما يلي موجه إلى فتاة:</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -638,7 +644,9 @@
           <t>ما يلي موجه إلى فتاة:</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.9270544648170471</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -661,7 +669,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>كم عمرك ؟</t>
+          <t>كم عمرك؟</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -680,7 +688,9 @@
           <t>كم عمرك؟</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.9216063022613525</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
+          <t>هذه كلمة بخط &lt;g1&gt;غامق&lt;/g1&gt;.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -513,12 +513,10 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>هذه كلمة بخط &lt;g1&gt;غامق&lt;/g1&gt;.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.8085042834281921</v>
-      </c>
+          <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,9 +554,7 @@
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>0.8854201436042786</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -600,9 +596,7 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>0.9105713367462158</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -641,12 +635,10 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ما يلي موجه إلى فتاة:</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9270544648170471</v>
-      </c>
+          <t>يتم توجيه ما يلي إلى فتاة:</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -685,12 +677,10 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>كم عمرك؟</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.9216063022613525</v>
-      </c>
+          <t>كم عمرك ؟</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>هذه كلمة بخط &lt;g1&gt;غامق&lt;/g1&gt;.</t>
+          <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -619,7 +619,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ما يلي موجه إلى فتاة:</t>
+          <t>يتم توجيه ما يلي إلى فتاة:</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>كم عمرك؟</t>
+          <t>كم عمرك ؟</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -516,7 +516,9 @@
           <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.5071795582771301</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,7 +556,9 @@
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.8854201436042786</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -596,7 +600,9 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.9105714559555054</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -638,7 +644,9 @@
           <t>يتم توجيه ما يلي إلى فتاة:</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.8859435319900513</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -680,7 +688,9 @@
           <t>كم عمرك ؟</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.9172203540802002</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -516,9 +516,7 @@
           <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0.5071795582771301</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,9 +554,7 @@
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>0.8854201436042786</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -600,9 +596,7 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>0.9105714559555054</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -644,9 +638,7 @@
           <t>يتم توجيه ما يلي إلى فتاة:</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>0.8859435319900513</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,9 +680,7 @@
           <t>كم عمرك ؟</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>0.9172203540802002</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -499,11 +499,7 @@
           <t>This is a &lt;g1&gt;bolded&lt;/g1&gt; word.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="b">
         <v>0</v>
@@ -537,11 +533,7 @@
           <t>This is my best sentence yet.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>هذه أفضل جملة لي حتى الآن.</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="b">
         <v>0</v>
@@ -575,11 +567,7 @@
           <t>This is a repeated sentence.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>هذه جملة مكررة.</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -617,11 +605,7 @@
           <t>The following is addressed to a girl:</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>يتم توجيه ما يلي إلى فتاة:</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -659,11 +643,7 @@
           <t>What is your age?</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>كم عمرك ؟</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>FIRST</t>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -499,7 +499,11 @@
           <t>This is a &lt;g1&gt;bolded&lt;/g1&gt; word.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="b">
         <v>0</v>
@@ -512,7 +516,9 @@
           <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.5071797966957092</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,7 +539,11 @@
           <t>This is my best sentence yet.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>هذه أفضل جملة لي حتى الآن.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="b">
         <v>0</v>
@@ -546,7 +556,9 @@
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.8854201436042786</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,7 +579,11 @@
           <t>This is a repeated sentence.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>هذه جملة مكررة.</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -584,7 +600,9 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.9105714559555054</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -605,7 +623,11 @@
           <t>The following is addressed to a girl:</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>يتم توجيه ما يلي إلى فتاة:</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -622,7 +644,9 @@
           <t>يتم توجيه ما يلي إلى فتاة:</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.8859433531761169</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -643,7 +667,11 @@
           <t>What is your age?</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>كم عمرك ؟</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -660,7 +688,9 @@
           <t>كم عمرك ؟</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.9172203540802002</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -499,11 +499,7 @@
           <t>This is a &lt;g1&gt;bolded&lt;/g1&gt; word.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="b">
         <v>0</v>
@@ -517,7 +513,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.5071797966957092</v>
+        <v>0.5071799755096436</v>
       </c>
     </row>
     <row r="3">
@@ -539,11 +535,7 @@
           <t>This is my best sentence yet.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>هذه أفضل جملة لي حتى الآن.</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="b">
         <v>0</v>
@@ -579,11 +571,7 @@
           <t>This is a repeated sentence.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>هذه جملة مكررة.</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -601,7 +589,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.9105714559555054</v>
+        <v>0.910571277141571</v>
       </c>
     </row>
     <row r="5">
@@ -623,11 +611,7 @@
           <t>The following is addressed to a girl:</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>يتم توجيه ما يلي إلى فتاة:</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -645,7 +629,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.8859433531761169</v>
+        <v>0.8859434723854065</v>
       </c>
     </row>
     <row r="6">
@@ -667,11 +651,7 @@
           <t>What is your age?</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>كم عمرك ؟</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>FIRST</t>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -499,7 +499,11 @@
           <t>This is a &lt;g1&gt;bolded&lt;/g1&gt; word.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="b">
         <v>0</v>
@@ -512,9 +516,7 @@
           <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0.5071799755096436</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -535,7 +537,11 @@
           <t>This is my best sentence yet.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>هذه أفضل جملة لي حتى الآن.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="b">
         <v>0</v>
@@ -548,9 +554,7 @@
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>0.8854201436042786</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -571,7 +575,11 @@
           <t>This is a repeated sentence.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>هذه جملة مكررة.</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -588,9 +596,7 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>0.910571277141571</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -611,7 +617,11 @@
           <t>The following is addressed to a girl:</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>يتم توجيه ما يلي إلى فتاة:</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -628,9 +638,7 @@
           <t>يتم توجيه ما يلي إلى فتاة:</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>0.8859434723854065</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -651,7 +659,11 @@
           <t>What is your age?</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>كم عمرك ؟</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>FIRST</t>
@@ -668,9 +680,7 @@
           <t>كم عمرك ؟</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>0.9172203540802002</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -516,7 +516,9 @@
           <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.5071800947189331</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,7 +556,9 @@
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.8854201436042786</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -596,7 +600,9 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.9105713963508606</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -638,7 +644,9 @@
           <t>يتم توجيه ما يلي إلى فتاة:</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.8859434723854065</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -680,7 +688,9 @@
           <t>كم عمرك ؟</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.9172202944755554</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
+          <t>Жжжж жж ж &lt;g1&gt;жжжжжж&lt;/g1&gt; жжжж.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -513,11 +513,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>هذه كلمة &lt;g1&gt;جريئة&lt;/g1&gt;.</t>
+          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.5071800947189331</v>
+        <v>0.8158649802207947</v>
       </c>
     </row>
     <row r="3">
@@ -541,7 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>هذه أفضل جملة لي حتى الآن.</t>
+          <t>Жжжж жж жж жжжж жжжжжжжж жжж.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -581,7 +581,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>هذه جملة مكررة.</t>
+          <t>Жжжж жж ж жжжжжжжж жжжжжжжж.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.9105713963508606</v>
+        <v>0.9105713367462158</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>يتم توجيه ما يلي إلى فتاة:</t>
+          <t>Жжж жжжжжжжжж жж жжжжжжжжж жж ж жжжж:</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -641,11 +641,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>يتم توجيه ما يلي إلى فتاة:</t>
+          <t>ما يلي موجه إلى فتاة:</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.8859434723854065</v>
+        <v>0.9270544648170471</v>
       </c>
     </row>
     <row r="6">
@@ -669,7 +669,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>كم عمرك ؟</t>
+          <t>Жжжж жж жжжж жжж?</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,11 +685,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>كم عمرك ؟</t>
+          <t>كم عمرك؟</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.9172202944755554</v>
+        <v>0.9216062426567078</v>
       </c>
     </row>
   </sheetData>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Жжжж жж ж &lt;g1&gt;жжжжжж&lt;/g1&gt; жжжж.</t>
+          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -541,7 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Жжжж жж жж жжжж жжжжжжжж жжж.</t>
+          <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -581,7 +581,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Жжжж жж ж жжжжжжжж жжжжжжжж.</t>
+          <t>هذه جملة مكررة.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Жжж жжжжжжжжж жж жжжжжжжжж жж ж жжжж:</t>
+          <t>ما يلي موجه إلى فتاة:</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Жжжж жж жжжж жжж?</t>
+          <t>كم عمرك؟</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.8854201436042786</v>
+        <v>0.8854200839996338</v>
       </c>
     </row>
     <row r="4">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.9105713367462158</v>
+        <v>0.9105713963508606</v>
       </c>
     </row>
     <row r="5">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.9216062426567078</v>
+        <v>0.9216063022613525</v>
       </c>
     </row>
   </sheetData>

--- a/mtpe/QE_scores.xlsx
+++ b/mtpe/QE_scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.8158649802207947</v>
+        <v>0.815865159034729</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.8854200839996338</v>
+        <v>0.8854202032089233</v>
       </c>
     </row>
     <row r="4">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.9105713963508606</v>
+        <v>0.9105714559555054</v>
       </c>
     </row>
     <row r="5">
@@ -689,7 +689,183 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.9216063022613525</v>
+        <v>0.9216064214706421</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>foo.xml</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4_0</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>This is a repeated sentence.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>هذه جملة مكررة.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>هذه جملة مكررة.</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9105714559555054</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>foo.xml</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5_0</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The following is addressed to a girl:</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ما يلي موجه إلى فتاة:</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ما يلي موجه إلى فتاة:</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9270544648170471</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>foo.xml</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6_0</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What is your age?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>كم عمرك؟</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>كم عمرك؟</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9216064214706421</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>foo.xml</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7_0</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>This is a repeated sentence.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>هذه جملة مكررة.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>هذه جملة مكررة.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9105714559555054</v>
       </c>
     </row>
   </sheetData>
